--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,6 +956,366 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123156495</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109041</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522918</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6458595</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123156496</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109250</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522834</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6458562</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123156492</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98990</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522913</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6458592</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156495</v>
+        <v>123178351</v>
       </c>
       <c r="B4" t="n">
-        <v>109041</v>
+        <v>109250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,26 +994,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522918</v>
+        <v>522894</v>
       </c>
       <c r="R4" t="n">
-        <v>6458595</v>
+        <v>6458585</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1041,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,7 +1061,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1081,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B5" t="n">
-        <v>109250</v>
+        <v>98990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,26 +1088,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1130,10 +1121,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R5" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1170,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,7 +1181,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1201,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156492</v>
+        <v>123178347</v>
       </c>
       <c r="B6" t="n">
-        <v>98990</v>
+        <v>99017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,31 +1208,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>222309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1250,10 +1236,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522913</v>
+        <v>522852</v>
       </c>
       <c r="R6" t="n">
-        <v>6458592</v>
+        <v>6458569</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1290,7 +1276,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,10 +1296,250 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123156496</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109250</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522834</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458562</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Melina Eberhagen</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123156495</v>
+      </c>
+      <c r="B8" t="n">
+        <v>109041</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandlyckan, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522918</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6458595</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Norra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,7 +961,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178351</v>
+        <v>123156496</v>
       </c>
       <c r="B4" t="n">
         <v>109250</v>
@@ -994,17 +994,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522894</v>
+        <v>522834</v>
       </c>
       <c r="R4" t="n">
-        <v>6458585</v>
+        <v>6458562</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1041,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156492</v>
+        <v>123156495</v>
       </c>
       <c r="B5" t="n">
-        <v>98990</v>
+        <v>109041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,26 +1097,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222295</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1121,10 +1130,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522913</v>
+        <v>522918</v>
       </c>
       <c r="R5" t="n">
-        <v>6458592</v>
+        <v>6458595</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1192,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178347</v>
+        <v>123178351</v>
       </c>
       <c r="B6" t="n">
-        <v>99017</v>
+        <v>109250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,38 +1217,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222309</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522852</v>
+        <v>522894</v>
       </c>
       <c r="R6" t="n">
-        <v>6458569</v>
+        <v>6458585</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1307,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B7" t="n">
-        <v>109250</v>
+        <v>98990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,26 +1328,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R7" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1396,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1432,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156495</v>
+        <v>123178347</v>
       </c>
       <c r="B8" t="n">
-        <v>109041</v>
+        <v>99017</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,31 +1448,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>222309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522918</v>
+        <v>522852</v>
       </c>
       <c r="R8" t="n">
-        <v>6458595</v>
+        <v>6458569</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156492</v>
+        <v>123178347</v>
       </c>
       <c r="B7" t="n">
-        <v>98990</v>
+        <v>99017</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,31 +1328,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222295</v>
+        <v>222309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522913</v>
+        <v>522852</v>
       </c>
       <c r="R7" t="n">
-        <v>6458592</v>
+        <v>6458569</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1401,7 +1396,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178347</v>
+        <v>123156492</v>
       </c>
       <c r="B8" t="n">
-        <v>99017</v>
+        <v>98990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,26 +1443,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222309</v>
+        <v>222295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522852</v>
+        <v>522913</v>
       </c>
       <c r="R8" t="n">
-        <v>6458569</v>
+        <v>6458592</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156496</v>
+        <v>123178347</v>
       </c>
       <c r="B4" t="n">
-        <v>109250</v>
+        <v>99017</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,31 +977,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522834</v>
+        <v>522852</v>
       </c>
       <c r="R4" t="n">
-        <v>6458562</v>
+        <v>6458569</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1045,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156495</v>
+        <v>123178351</v>
       </c>
       <c r="B5" t="n">
-        <v>109041</v>
+        <v>109250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,16 +1092,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1114,26 +1109,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522918</v>
+        <v>522894</v>
       </c>
       <c r="R5" t="n">
-        <v>6458595</v>
+        <v>6458585</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1170,7 +1156,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1201,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178351</v>
+        <v>123156495</v>
       </c>
       <c r="B6" t="n">
-        <v>109250</v>
+        <v>109041</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,16 +1203,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1234,17 +1220,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522894</v>
+        <v>522918</v>
       </c>
       <c r="R6" t="n">
-        <v>6458585</v>
+        <v>6458595</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,7 +1276,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123178347</v>
+        <v>123156496</v>
       </c>
       <c r="B7" t="n">
-        <v>99017</v>
+        <v>109250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,26 +1323,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222309</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522852</v>
+        <v>522834</v>
       </c>
       <c r="R7" t="n">
-        <v>6458569</v>
+        <v>6458562</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178347</v>
+        <v>123156495</v>
       </c>
       <c r="B4" t="n">
-        <v>99017</v>
+        <v>109041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,26 +977,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222309</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522852</v>
+        <v>522918</v>
       </c>
       <c r="R4" t="n">
-        <v>6458569</v>
+        <v>6458595</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1045,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178351</v>
+        <v>123178347</v>
       </c>
       <c r="B5" t="n">
-        <v>109250</v>
+        <v>99017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,34 +1097,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>222309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522894</v>
+        <v>522852</v>
       </c>
       <c r="R5" t="n">
-        <v>6458585</v>
+        <v>6458569</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1187,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156495</v>
+        <v>123156492</v>
       </c>
       <c r="B6" t="n">
-        <v>109041</v>
+        <v>98990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,26 +1212,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>222295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1236,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522918</v>
+        <v>522913</v>
       </c>
       <c r="R6" t="n">
-        <v>6458595</v>
+        <v>6458592</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1427,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156492</v>
+        <v>123178351</v>
       </c>
       <c r="B8" t="n">
-        <v>98990</v>
+        <v>109250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,43 +1452,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222295</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522913</v>
+        <v>522894</v>
       </c>
       <c r="R8" t="n">
-        <v>6458592</v>
+        <v>6458585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156495</v>
+        <v>123178347</v>
       </c>
       <c r="B4" t="n">
-        <v>109041</v>
+        <v>99020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,31 +977,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>222309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522918</v>
+        <v>522852</v>
       </c>
       <c r="R4" t="n">
-        <v>6458595</v>
+        <v>6458569</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1045,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178347</v>
+        <v>123156495</v>
       </c>
       <c r="B5" t="n">
-        <v>99017</v>
+        <v>109045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,26 +1092,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222309</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522852</v>
+        <v>522918</v>
       </c>
       <c r="R5" t="n">
-        <v>6458569</v>
+        <v>6458595</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156492</v>
+        <v>123156496</v>
       </c>
       <c r="B6" t="n">
-        <v>98990</v>
+        <v>109254</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,26 +1212,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522913</v>
+        <v>522834</v>
       </c>
       <c r="R6" t="n">
-        <v>6458592</v>
+        <v>6458562</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B7" t="n">
-        <v>109250</v>
+        <v>98993</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,26 +1332,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R7" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,7 +1439,7 @@
         <v>123178351</v>
       </c>
       <c r="B8" t="n">
-        <v>109250</v>
+        <v>109254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178347</v>
+        <v>123156496</v>
       </c>
       <c r="B4" t="n">
-        <v>99020</v>
+        <v>109256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,26 +977,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222309</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522852</v>
+        <v>522834</v>
       </c>
       <c r="R4" t="n">
-        <v>6458569</v>
+        <v>6458562</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1045,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156495</v>
+        <v>123178351</v>
       </c>
       <c r="B5" t="n">
-        <v>109045</v>
+        <v>109256</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,16 +1097,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1109,26 +1114,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522918</v>
+        <v>522894</v>
       </c>
       <c r="R5" t="n">
-        <v>6458595</v>
+        <v>6458585</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1165,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B6" t="n">
-        <v>109254</v>
+        <v>98995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,26 +1208,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1245,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R6" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1285,7 +1281,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156492</v>
+        <v>123156495</v>
       </c>
       <c r="B7" t="n">
-        <v>98993</v>
+        <v>109047</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,26 +1328,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222295</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1365,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522913</v>
+        <v>522918</v>
       </c>
       <c r="R7" t="n">
-        <v>6458592</v>
+        <v>6458595</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1436,10 +1432,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178351</v>
+        <v>123178347</v>
       </c>
       <c r="B8" t="n">
-        <v>109254</v>
+        <v>99022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,34 +1448,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>222309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522894</v>
+        <v>522852</v>
       </c>
       <c r="R8" t="n">
-        <v>6458585</v>
+        <v>6458569</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156496</v>
+        <v>123178351</v>
       </c>
       <c r="B4" t="n">
-        <v>109256</v>
+        <v>109262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -994,26 +994,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522834</v>
+        <v>522894</v>
       </c>
       <c r="R4" t="n">
-        <v>6458562</v>
+        <v>6458585</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1041,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178351</v>
+        <v>123178347</v>
       </c>
       <c r="B5" t="n">
-        <v>109256</v>
+        <v>99028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,34 +1088,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>222309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522894</v>
+        <v>522852</v>
       </c>
       <c r="R5" t="n">
-        <v>6458585</v>
+        <v>6458569</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1192,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156492</v>
+        <v>123156495</v>
       </c>
       <c r="B6" t="n">
-        <v>98995</v>
+        <v>109053</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,26 +1203,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1241,10 +1236,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522913</v>
+        <v>522918</v>
       </c>
       <c r="R6" t="n">
-        <v>6458592</v>
+        <v>6458595</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1312,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156495</v>
+        <v>123156492</v>
       </c>
       <c r="B7" t="n">
-        <v>109047</v>
+        <v>99001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,26 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>222295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522918</v>
+        <v>522913</v>
       </c>
       <c r="R7" t="n">
-        <v>6458595</v>
+        <v>6458592</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1432,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178347</v>
+        <v>123156496</v>
       </c>
       <c r="B8" t="n">
-        <v>99022</v>
+        <v>109262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,26 +1443,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222309</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522852</v>
+        <v>522834</v>
       </c>
       <c r="R8" t="n">
-        <v>6458569</v>
+        <v>6458562</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -964,7 +964,7 @@
         <v>123178351</v>
       </c>
       <c r="B4" t="n">
-        <v>109262</v>
+        <v>109265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>123178347</v>
       </c>
       <c r="B5" t="n">
-        <v>99028</v>
+        <v>99031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>123156495</v>
       </c>
       <c r="B6" t="n">
-        <v>109053</v>
+        <v>109056</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156492</v>
+        <v>123156496</v>
       </c>
       <c r="B7" t="n">
-        <v>99001</v>
+        <v>109265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,26 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222295</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522913</v>
+        <v>522834</v>
       </c>
       <c r="R7" t="n">
-        <v>6458592</v>
+        <v>6458562</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B8" t="n">
-        <v>109262</v>
+        <v>99004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,26 +1443,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R8" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178351</v>
+        <v>123156496</v>
       </c>
       <c r="B4" t="n">
-        <v>109265</v>
+        <v>109282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -994,17 +994,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522894</v>
+        <v>522834</v>
       </c>
       <c r="R4" t="n">
-        <v>6458585</v>
+        <v>6458562</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1041,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,7 +1084,7 @@
         <v>123178347</v>
       </c>
       <c r="B5" t="n">
-        <v>99031</v>
+        <v>99048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1187,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156495</v>
+        <v>123156492</v>
       </c>
       <c r="B6" t="n">
-        <v>109056</v>
+        <v>99021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,26 +1212,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>222295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1236,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522918</v>
+        <v>522913</v>
       </c>
       <c r="R6" t="n">
-        <v>6458595</v>
+        <v>6458592</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1307,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156496</v>
+        <v>123156495</v>
       </c>
       <c r="B7" t="n">
-        <v>109265</v>
+        <v>109073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,16 +1332,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1342,7 +1351,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1356,10 +1365,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522834</v>
+        <v>522918</v>
       </c>
       <c r="R7" t="n">
-        <v>6458562</v>
+        <v>6458595</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1396,7 +1405,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156492</v>
+        <v>123178351</v>
       </c>
       <c r="B8" t="n">
-        <v>99004</v>
+        <v>109282</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,43 +1452,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222295</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522913</v>
+        <v>522894</v>
       </c>
       <c r="R8" t="n">
-        <v>6458592</v>
+        <v>6458585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -961,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B4" t="n">
-        <v>109282</v>
+        <v>99127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,26 +977,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R4" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1084,7 +1084,7 @@
         <v>123178347</v>
       </c>
       <c r="B5" t="n">
-        <v>99048</v>
+        <v>99154</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156492</v>
+        <v>123178351</v>
       </c>
       <c r="B6" t="n">
-        <v>99021</v>
+        <v>109300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,43 +1212,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522913</v>
+        <v>522894</v>
       </c>
       <c r="R6" t="n">
-        <v>6458592</v>
+        <v>6458585</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1285,7 +1276,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156495</v>
+        <v>123156496</v>
       </c>
       <c r="B7" t="n">
-        <v>109073</v>
+        <v>109300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,16 +1323,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1351,7 +1342,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1365,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522918</v>
+        <v>522834</v>
       </c>
       <c r="R7" t="n">
-        <v>6458595</v>
+        <v>6458562</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1405,7 +1396,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178351</v>
+        <v>123156495</v>
       </c>
       <c r="B8" t="n">
-        <v>109282</v>
+        <v>109091</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,16 +1443,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1469,17 +1460,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522894</v>
+        <v>522918</v>
       </c>
       <c r="R8" t="n">
-        <v>6458585</v>
+        <v>6458595</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,67 +816,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98842722</v>
+        <v>123156492</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
+        <v>99129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandlyckan, 250 m O, Ög</t>
+          <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522938.2681942342</v>
+        <v>522913</v>
       </c>
       <c r="R3" t="n">
-        <v>6458661.479405164</v>
+        <v>6458592</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,34 +893,19 @@
           <t>Gammalkil</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>E-Lin-0827</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spridda inom området</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,35 +916,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>mossiga stenar i granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Melina Eberhagen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anita Sjö</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156492</v>
+        <v>123156495</v>
       </c>
       <c r="B4" t="n">
-        <v>99127</v>
+        <v>109093</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,26 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222295</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1010,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522913</v>
+        <v>522918</v>
       </c>
       <c r="R4" t="n">
-        <v>6458592</v>
+        <v>6458595</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1081,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178347</v>
+        <v>123178351</v>
       </c>
       <c r="B5" t="n">
-        <v>99154</v>
+        <v>109302</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,38 +1072,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222309</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522852</v>
+        <v>522894</v>
       </c>
       <c r="R5" t="n">
-        <v>6458569</v>
+        <v>6458585</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1196,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178351</v>
+        <v>123178347</v>
       </c>
       <c r="B6" t="n">
-        <v>109300</v>
+        <v>99156</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,34 +1183,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>222309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522894</v>
+        <v>522852</v>
       </c>
       <c r="R6" t="n">
-        <v>6458585</v>
+        <v>6458569</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1310,7 +1285,7 @@
         <v>123156496</v>
       </c>
       <c r="B7" t="n">
-        <v>109300</v>
+        <v>109302</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1420,126 +1395,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>123156495</v>
-      </c>
-      <c r="B8" t="n">
-        <v>109091</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220228</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sommarfibbla</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Leontodon hispidus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Sandlyckan, Ög</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>522918</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6458595</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Linköping</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Gammalkil</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Norra vägsidan, ytterslänt</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Melina Eberhagen</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Via Melina Eberhagen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 61915-2024 artfynd.xlsx
+++ b/artfynd/A 61915-2024 artfynd.xlsx
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156492</v>
+        <v>123178351</v>
       </c>
       <c r="B3" t="n">
-        <v>99129</v>
+        <v>108877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,43 +832,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222295</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522913</v>
+        <v>522894</v>
       </c>
       <c r="R3" t="n">
-        <v>6458592</v>
+        <v>6458585</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +896,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156495</v>
+        <v>123178347</v>
       </c>
       <c r="B4" t="n">
-        <v>109093</v>
+        <v>98731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,31 +943,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>222309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -985,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522918</v>
+        <v>522852</v>
       </c>
       <c r="R4" t="n">
-        <v>6458595</v>
+        <v>6458569</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1025,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra vägsidan, ytterslänt</t>
+          <t>Norra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178351</v>
+        <v>123156495</v>
       </c>
       <c r="B5" t="n">
-        <v>109302</v>
+        <v>108668</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,16 +1058,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1089,17 +1075,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandlyckan, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522894</v>
+        <v>522918</v>
       </c>
       <c r="R5" t="n">
-        <v>6458585</v>
+        <v>6458595</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1136,7 +1131,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178347</v>
+        <v>123156496</v>
       </c>
       <c r="B6" t="n">
-        <v>99156</v>
+        <v>108877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,26 +1178,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222309</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522852</v>
+        <v>522834</v>
       </c>
       <c r="R6" t="n">
-        <v>6458569</v>
+        <v>6458562</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägsidan, hela vägområdet</t>
+          <t>Norra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156496</v>
+        <v>123156492</v>
       </c>
       <c r="B7" t="n">
-        <v>109302</v>
+        <v>98704</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,26 +1298,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522834</v>
+        <v>522913</v>
       </c>
       <c r="R7" t="n">
-        <v>6458562</v>
+        <v>6458592</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Norra vägsidan, innerslänt</t>
+          <t>Norra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
